--- a/excel/Rule_Tracking.xlsx
+++ b/excel/Rule_Tracking.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
   <si>
     <t>Date</t>
   </si>
@@ -55,7 +55,7 @@
     <t>❌</t>
   </si>
   <si>
-    <t>Sat, Jul 20, 2025</t>
+    <t>Sun, Aug 10, 2025</t>
   </si>
 </sst>
 </file>
@@ -162,11 +162,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -488,66 +485,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="C2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="I3" s="6" t="s">
-        <v>12</v>
-      </c>
+      <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="18">
-      <c r="B4" s="5"/>
+      <c r="B4" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
